--- a/uloha8/uloha8.xlsx
+++ b/uloha8/uloha8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C191F359-AFD8-4E29-8092-D0248BECB552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996B3F77-1612-46C5-8905-52BFE35E31C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D89BB8E-BAF2-48F1-8549-58BD16157EFC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>A</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>f_2 / kHz</t>
+  </si>
+  <si>
+    <t>w_r^-2 / 10^-14 s^-2</t>
   </si>
 </sst>
 </file>
@@ -260,7 +263,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>w_r^-2 / 10^4 s^-2</c:v>
+                  <c:v>w_r^-2 / 10^-14 s^-2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -376,19 +379,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>538.49592427132825</c:v>
+                  <c:v>5.3849592427132826</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>955.97724006008673</c:v>
+                  <c:v>9.5597724006008686</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1373.4569430369377</c:v>
+                  <c:v>13.734569430369376</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1789.3168268196496</c:v>
+                  <c:v>17.893168268196497</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2206.7516498973955</c:v>
+                  <c:v>22.067516498973959</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -782,7 +785,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>w_r^-2 / 10^4 s^-2</c:v>
+                  <c:v>w_r^-2 / 10^-14 s^-2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -898,19 +901,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>551.11842821554671</c:v>
+                  <c:v>5.5111842821554662</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1049.6273451216066</c:v>
+                  <c:v>10.496273451216068</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1548.8807043405238</c:v>
+                  <c:v>15.48880704340524</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2044.9294252618483</c:v>
+                  <c:v>20.449294252618483</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2541.5057669252578</c:v>
+                  <c:v>25.41505766925258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6260,7 +6263,7 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
         <v>5</v>
@@ -6302,8 +6305,8 @@
         <v>200</v>
       </c>
       <c r="E3">
-        <f>(2*3.1415926536*A3)^-2*10^10</f>
-        <v>538.49592427132825</v>
+        <f>(2*3.1415926536*A3)^-2*10^8</f>
+        <v>5.3849592427132826</v>
       </c>
       <c r="G3" t="s">
         <v>6</v>
@@ -6363,8 +6366,8 @@
         <v>400</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E7" si="3">(2*3.1415926536*A4)^-2*10^10</f>
-        <v>955.97724006008673</v>
+        <f t="shared" ref="E4:E7" si="3">(2*3.1415926536*A4)^-2*10^8</f>
+        <v>9.5597724006008686</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -6436,7 +6439,7 @@
       </c>
       <c r="E5">
         <f t="shared" si="3"/>
-        <v>1373.4569430369377</v>
+        <v>13.734569430369376</v>
       </c>
       <c r="K5">
         <f t="shared" ref="K5:K8" si="5">AVERAGE(L5,M5)</f>
@@ -6506,7 +6509,7 @@
       </c>
       <c r="E6">
         <f t="shared" si="3"/>
-        <v>1789.3168268196496</v>
+        <v>17.893168268196497</v>
       </c>
       <c r="K6">
         <f t="shared" si="5"/>
@@ -6560,7 +6563,7 @@
       </c>
       <c r="E7">
         <f t="shared" si="3"/>
-        <v>2206.7516498973955</v>
+        <v>22.067516498973959</v>
       </c>
       <c r="K7">
         <f t="shared" si="5"/>
@@ -6995,7 +6998,7 @@
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K26" t="s">
         <v>20</v>
@@ -7046,8 +7049,8 @@
         <v>200</v>
       </c>
       <c r="F27">
-        <f>(2*3.1415926536*B27)^-2*10^10</f>
-        <v>551.11842821554671</v>
+        <f>(2*3.1415926536*B27)^-2*10^8</f>
+        <v>5.5111842821554662</v>
       </c>
       <c r="K27">
         <f>AVERAGE(L27,M27)</f>
@@ -7100,8 +7103,8 @@
         <v>400</v>
       </c>
       <c r="F28">
-        <f t="shared" ref="F28:F31" si="8">(2*3.1415926536*B28)^-2*10^10</f>
-        <v>1049.6273451216066</v>
+        <f t="shared" ref="F28:F31" si="8">(2*3.1415926536*B28)^-2*10^8</f>
+        <v>10.496273451216068</v>
       </c>
       <c r="K28">
         <f t="shared" ref="K28:K31" si="9">AVERAGE(L28,M28)</f>
@@ -7155,7 +7158,7 @@
       </c>
       <c r="F29">
         <f t="shared" si="8"/>
-        <v>1548.8807043405238</v>
+        <v>15.48880704340524</v>
       </c>
       <c r="K29">
         <f t="shared" si="9"/>
@@ -7209,7 +7212,7 @@
       </c>
       <c r="F30">
         <f t="shared" si="8"/>
-        <v>2044.9294252618483</v>
+        <v>20.449294252618483</v>
       </c>
       <c r="K30">
         <f t="shared" si="9"/>
@@ -7263,7 +7266,7 @@
       </c>
       <c r="F31">
         <f t="shared" si="8"/>
-        <v>2541.5057669252578</v>
+        <v>25.41505766925258</v>
       </c>
       <c r="K31">
         <f t="shared" si="9"/>
@@ -7344,7 +7347,7 @@
       </c>
       <c r="D3">
         <f>List1!E3</f>
-        <v>538.49592427132825</v>
+        <v>5.3849592427132826</v>
       </c>
       <c r="E3">
         <f>List1!D3</f>
@@ -7360,7 +7363,7 @@
       </c>
       <c r="D4">
         <f>List1!E4</f>
-        <v>955.97724006008673</v>
+        <v>9.5597724006008686</v>
       </c>
       <c r="E4">
         <f>List1!D4</f>
@@ -7376,7 +7379,7 @@
       </c>
       <c r="D5">
         <f>List1!E5</f>
-        <v>1373.4569430369377</v>
+        <v>13.734569430369376</v>
       </c>
       <c r="E5">
         <f>List1!D5</f>
@@ -7392,7 +7395,7 @@
       </c>
       <c r="D6">
         <f>List1!E6</f>
-        <v>1789.3168268196496</v>
+        <v>17.893168268196497</v>
       </c>
       <c r="E6">
         <f>List1!D6</f>
@@ -7408,7 +7411,7 @@
       </c>
       <c r="D7">
         <f>List1!E7</f>
-        <v>2206.7516498973955</v>
+        <v>22.067516498973959</v>
       </c>
       <c r="E7">
         <f>List1!D7</f>

--- a/uloha8/uloha8.xlsx
+++ b/uloha8/uloha8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996B3F77-1612-46C5-8905-52BFE35E31C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC03746-322D-4D18-BFC0-575F790C2BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D89BB8E-BAF2-48F1-8549-58BD16157EFC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
   <si>
     <t>A</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Q</t>
   </si>
   <si>
-    <t>w_r^-2 / 10^4 s^-2</t>
-  </si>
-  <si>
     <t>C_N / pF</t>
   </si>
   <si>
@@ -124,6 +121,9 @@
   </si>
   <si>
     <t>w_r^-2 / 10^-14 s^-2</t>
+  </si>
+  <si>
+    <t>Rs</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1316,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>w_r^-2 / 10^4 s^-2</c:v>
+                  <c:v>w_r^-2 / 10^-14 s^-2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1432,19 +1432,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>773.65004715208624</c:v>
+                  <c:v>7.7365004715208618</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1469.7050240112994</c:v>
+                  <c:v>14.697050240112993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2166.9159269898887</c:v>
+                  <c:v>21.669159269898888</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2859.0943645509683</c:v>
+                  <c:v>28.590943645509686</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3554.5155042415099</c:v>
+                  <c:v>35.545155042415097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1848,7 +1848,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>w_r^-2 / 10^4 s^-2</c:v>
+                  <c:v>w_r^-2 / 10^-14 s^-2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1964,19 +1964,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1247.2729750171927</c:v>
+                  <c:v>12.472729750171926</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2369.613851743828</c:v>
+                  <c:v>23.696138517438282</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3496.644618081777</c:v>
+                  <c:v>34.966446180817769</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4614.192257177071</c:v>
+                  <c:v>46.141922571770706</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5735.6345821710556</c:v>
+                  <c:v>57.356345821710555</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6235,13 +6235,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8383762E-D7D8-4727-91B3-7DC3C52B8287}">
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6249,21 +6249,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
       </c>
       <c r="G2" t="s">
         <v>5</v>
@@ -6275,7 +6275,7 @@
         <v>2</v>
       </c>
       <c r="S2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T2" t="s">
         <v>11</v>
@@ -6290,7 +6290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>AVERAGE(B3,C3)</f>
         <v>685.84965</v>
@@ -6318,19 +6318,19 @@
         <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" t="s">
         <v>27</v>
-      </c>
-      <c r="N3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" t="s">
-        <v>18</v>
       </c>
       <c r="S3">
         <v>218.8</v>
@@ -6350,8 +6350,12 @@
         <f t="shared" ref="W3:W31" si="1">V3/MAX($V$3:$V$31)</f>
         <v>2.44140625E-2</v>
       </c>
+      <c r="X3">
+        <f>U3/MAX($U$3:$U$31)</f>
+        <v>0.15625</v>
+      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ref="A4:A7" si="2">AVERAGE(B4,C4)</f>
         <v>514.75</v>
@@ -6389,8 +6393,8 @@
         <v>200</v>
       </c>
       <c r="O4">
-        <f>(2*3.1415926536*K4)^-2*10^10</f>
-        <v>773.65004715208624</v>
+        <f>(2*3.1415926536*K4)^-2*10^8</f>
+        <v>7.7365004715208618</v>
       </c>
       <c r="S4">
         <v>217.3</v>
@@ -6410,20 +6414,27 @@
         <f t="shared" si="1"/>
         <v>4.78515625E-2</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4">
+        <f t="shared" ref="X4:X31" si="5">U4/MAX($U$3:$U$31)</f>
+        <v>0.21875</v>
+      </c>
+      <c r="Y4" t="s">
         <v>14</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>15</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>16</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>17</v>
       </c>
+      <c r="AC4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="2"/>
         <v>429.45</v>
@@ -6442,7 +6453,7 @@
         <v>13.734569430369376</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K8" si="5">AVERAGE(L5,M5)</f>
+        <f t="shared" ref="K5:K8" si="6">AVERAGE(L5,M5)</f>
         <v>415.15</v>
       </c>
       <c r="L5">
@@ -6455,8 +6466,8 @@
         <v>400</v>
       </c>
       <c r="O5">
-        <f t="shared" ref="O5:O8" si="6">(2*3.1415926536*K5)^-2*10^10</f>
-        <v>1469.7050240112994</v>
+        <f t="shared" ref="O5:O8" si="7">(2*3.1415926536*K5)^-2*10^8</f>
+        <v>14.697050240112993</v>
       </c>
       <c r="S5">
         <v>216.2</v>
@@ -6477,23 +6488,31 @@
         <v>7.91015625E-2</v>
       </c>
       <c r="X5">
-        <f>T12</f>
-        <v>1.0111824886985485</v>
+        <f t="shared" si="5"/>
+        <v>0.28125</v>
       </c>
       <c r="Y5">
-        <f>T22</f>
-        <v>0.98881751130145135</v>
+        <f>T8</f>
+        <v>1.019271948608137</v>
       </c>
       <c r="Z5">
-        <f>X5-Y5</f>
-        <v>2.2364977397097197E-2</v>
+        <f>T25</f>
+        <v>0.98310730430644777</v>
       </c>
       <c r="AA5">
-        <f>1/Z5</f>
-        <v>44.71276595744704</v>
+        <f>Y5-Z5</f>
+        <v>3.6164644301689197E-2</v>
+      </c>
+      <c r="AB5">
+        <f>1/AA5</f>
+        <v>27.651315789473738</v>
+      </c>
+      <c r="AC5">
+        <f>AA5*2*3.14159265*K31*0.561</f>
+        <v>26.788988845079949</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="2"/>
         <v>376.25</v>
@@ -6512,7 +6531,7 @@
         <v>17.893168268196497</v>
       </c>
       <c r="K6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>341.9</v>
       </c>
       <c r="L6">
@@ -6525,8 +6544,8 @@
         <v>600</v>
       </c>
       <c r="O6">
-        <f t="shared" si="6"/>
-        <v>2166.9159269898887</v>
+        <f t="shared" si="7"/>
+        <v>21.669159269898888</v>
       </c>
       <c r="S6">
         <v>215.4</v>
@@ -6546,8 +6565,12 @@
         <f t="shared" si="1"/>
         <v>0.1181640625</v>
       </c>
+      <c r="X6">
+        <f t="shared" si="5"/>
+        <v>0.34375</v>
+      </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="2"/>
         <v>338.79999999999995</v>
@@ -6566,7 +6589,7 @@
         <v>22.067516498973959</v>
       </c>
       <c r="K7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>297.64999999999998</v>
       </c>
       <c r="L7">
@@ -6579,8 +6602,8 @@
         <v>800</v>
       </c>
       <c r="O7">
-        <f t="shared" si="6"/>
-        <v>2859.0943645509683</v>
+        <f t="shared" si="7"/>
+        <v>28.590943645509686</v>
       </c>
       <c r="S7">
         <v>214.8</v>
@@ -6600,10 +6623,14 @@
         <f t="shared" si="1"/>
         <v>0.1650390625</v>
       </c>
+      <c r="X7">
+        <f t="shared" si="5"/>
+        <v>0.40625</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="K8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>266.95</v>
       </c>
       <c r="L8">
@@ -6616,8 +6643,8 @@
         <v>1000</v>
       </c>
       <c r="O8">
-        <f t="shared" si="6"/>
-        <v>3554.5155042415099</v>
+        <f t="shared" si="7"/>
+        <v>35.545155042415097</v>
       </c>
       <c r="S8">
         <v>214.2</v>
@@ -6637,8 +6664,12 @@
         <f t="shared" si="1"/>
         <v>0.2197265625</v>
       </c>
+      <c r="X8">
+        <f t="shared" si="5"/>
+        <v>0.46875</v>
+      </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="S9">
         <v>213.7</v>
       </c>
@@ -6657,8 +6688,12 @@
         <f t="shared" si="1"/>
         <v>0.2822265625</v>
       </c>
+      <c r="X9">
+        <f t="shared" si="5"/>
+        <v>0.53125</v>
+      </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="S10">
         <v>213.3</v>
       </c>
@@ -6677,8 +6712,12 @@
         <f t="shared" si="1"/>
         <v>0.3525390625</v>
       </c>
+      <c r="X10">
+        <f t="shared" si="5"/>
+        <v>0.59375</v>
+      </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="S11">
         <v>212.9</v>
       </c>
@@ -6697,8 +6736,12 @@
         <f t="shared" si="1"/>
         <v>0.4306640625</v>
       </c>
+      <c r="X11">
+        <f t="shared" si="5"/>
+        <v>0.65625</v>
+      </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="S12">
         <v>212.5</v>
       </c>
@@ -6717,8 +6760,12 @@
         <f t="shared" si="1"/>
         <v>0.5166015625</v>
       </c>
+      <c r="X12">
+        <f t="shared" si="5"/>
+        <v>0.71875</v>
+      </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="S13">
         <v>212.2</v>
       </c>
@@ -6737,8 +6784,12 @@
         <f t="shared" si="1"/>
         <v>0.6103515625</v>
       </c>
+      <c r="X13">
+        <f t="shared" si="5"/>
+        <v>0.78125</v>
+      </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="S14">
         <v>211.8</v>
       </c>
@@ -6757,8 +6808,12 @@
         <f t="shared" si="1"/>
         <v>0.7119140625</v>
       </c>
+      <c r="X14">
+        <f t="shared" si="5"/>
+        <v>0.84375</v>
+      </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="S15">
         <v>211.4</v>
       </c>
@@ -6777,8 +6832,12 @@
         <f t="shared" si="1"/>
         <v>0.8212890625</v>
       </c>
+      <c r="X15">
+        <f t="shared" si="5"/>
+        <v>0.90625</v>
+      </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="S16">
         <v>210.8</v>
       </c>
@@ -6797,8 +6856,12 @@
         <f t="shared" si="1"/>
         <v>0.9384765625</v>
       </c>
+      <c r="X16">
+        <f t="shared" si="5"/>
+        <v>0.96875</v>
+      </c>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
       <c r="S17">
         <v>210.3</v>
       </c>
@@ -6817,8 +6880,12 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
+      <c r="X17">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.3">
       <c r="S18">
         <v>209.5</v>
       </c>
@@ -6837,8 +6904,12 @@
         <f t="shared" si="1"/>
         <v>0.9384765625</v>
       </c>
+      <c r="X18">
+        <f t="shared" si="5"/>
+        <v>0.96875</v>
+      </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.3">
       <c r="S19">
         <v>209</v>
       </c>
@@ -6857,8 +6928,12 @@
         <f t="shared" si="1"/>
         <v>0.8212890625</v>
       </c>
+      <c r="X19">
+        <f t="shared" si="5"/>
+        <v>0.90625</v>
+      </c>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.3">
       <c r="S20">
         <v>208.6</v>
       </c>
@@ -6877,8 +6952,12 @@
         <f t="shared" si="1"/>
         <v>0.7119140625</v>
       </c>
+      <c r="X20">
+        <f t="shared" si="5"/>
+        <v>0.84375</v>
+      </c>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
       <c r="S21">
         <v>208.2</v>
       </c>
@@ -6897,8 +6976,12 @@
         <f t="shared" si="1"/>
         <v>0.6103515625</v>
       </c>
+      <c r="X21">
+        <f t="shared" si="5"/>
+        <v>0.78125</v>
+      </c>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.3">
       <c r="S22">
         <v>207.8</v>
       </c>
@@ -6917,8 +7000,12 @@
         <f t="shared" si="1"/>
         <v>0.5166015625</v>
       </c>
+      <c r="X22">
+        <f t="shared" si="5"/>
+        <v>0.71875</v>
+      </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.3">
       <c r="S23">
         <v>207.4</v>
       </c>
@@ -6937,8 +7024,12 @@
         <f t="shared" si="1"/>
         <v>0.4306640625</v>
       </c>
+      <c r="X23">
+        <f t="shared" si="5"/>
+        <v>0.65625</v>
+      </c>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.3">
       <c r="S24">
         <v>207</v>
       </c>
@@ -6957,8 +7048,12 @@
         <f t="shared" si="1"/>
         <v>0.3525390625</v>
       </c>
+      <c r="X24">
+        <f t="shared" si="5"/>
+        <v>0.59375</v>
+      </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>1</v>
       </c>
@@ -6983,37 +7078,41 @@
         <f t="shared" si="1"/>
         <v>0.2822265625</v>
       </c>
+      <c r="X25">
+        <f t="shared" si="5"/>
+        <v>0.53125</v>
+      </c>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
         <v>26</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
         <v>27</v>
       </c>
-      <c r="E26" t="s">
+      <c r="K26" t="s">
         <v>19</v>
       </c>
-      <c r="F26" t="s">
-        <v>28</v>
-      </c>
-      <c r="K26" t="s">
-        <v>20</v>
-      </c>
       <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" t="s">
         <v>26</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" t="s">
         <v>27</v>
-      </c>
-      <c r="N26" t="s">
-        <v>19</v>
-      </c>
-      <c r="O26" t="s">
-        <v>18</v>
       </c>
       <c r="S26">
         <v>206.2</v>
@@ -7033,8 +7132,12 @@
         <f t="shared" si="1"/>
         <v>0.2197265625</v>
       </c>
+      <c r="X26">
+        <f t="shared" si="5"/>
+        <v>0.46875</v>
+      </c>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B27">
         <f>AVERAGE(C27,D27)</f>
         <v>677.95</v>
@@ -7066,8 +7169,8 @@
         <v>200</v>
       </c>
       <c r="O27">
-        <f>(2*3.1415926536*K27)^-2*10^10</f>
-        <v>1247.2729750171927</v>
+        <f>(2*3.1415926536*K27)^-2*10^8</f>
+        <v>12.472729750171926</v>
       </c>
       <c r="S27">
         <v>205.6</v>
@@ -7087,10 +7190,14 @@
         <f t="shared" si="1"/>
         <v>0.1650390625</v>
       </c>
+      <c r="X27">
+        <f t="shared" si="5"/>
+        <v>0.40625</v>
+      </c>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B28">
-        <f t="shared" ref="B28:B31" si="7">AVERAGE(C28,D28)</f>
+        <f t="shared" ref="B28:B31" si="8">AVERAGE(C28,D28)</f>
         <v>491.25</v>
       </c>
       <c r="C28">
@@ -7103,11 +7210,11 @@
         <v>400</v>
       </c>
       <c r="F28">
-        <f t="shared" ref="F28:F31" si="8">(2*3.1415926536*B28)^-2*10^8</f>
+        <f t="shared" ref="F28:F31" si="9">(2*3.1415926536*B28)^-2*10^8</f>
         <v>10.496273451216068</v>
       </c>
       <c r="K28">
-        <f t="shared" ref="K28:K31" si="9">AVERAGE(L28,M28)</f>
+        <f t="shared" ref="K28:K31" si="10">AVERAGE(L28,M28)</f>
         <v>326.95000000000005</v>
       </c>
       <c r="L28">
@@ -7120,8 +7227,8 @@
         <v>400</v>
       </c>
       <c r="O28">
-        <f t="shared" ref="O28:O31" si="10">(2*3.1415926536*K28)^-2*10^10</f>
-        <v>2369.613851743828</v>
+        <f t="shared" ref="O28:O31" si="11">(2*3.1415926536*K28)^-2*10^8</f>
+        <v>23.696138517438282</v>
       </c>
       <c r="S28">
         <v>204.9</v>
@@ -7141,10 +7248,14 @@
         <f t="shared" si="1"/>
         <v>0.1181640625</v>
       </c>
+      <c r="X28">
+        <f t="shared" si="5"/>
+        <v>0.34375</v>
+      </c>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B29">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>404.4</v>
       </c>
       <c r="C29">
@@ -7157,11 +7268,11 @@
         <v>600</v>
       </c>
       <c r="F29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>15.48880704340524</v>
       </c>
       <c r="K29">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>269.14999999999998</v>
       </c>
       <c r="L29">
@@ -7174,8 +7285,8 @@
         <v>600</v>
       </c>
       <c r="O29">
-        <f t="shared" si="10"/>
-        <v>3496.644618081777</v>
+        <f t="shared" si="11"/>
+        <v>34.966446180817769</v>
       </c>
       <c r="S29">
         <v>204.2</v>
@@ -7195,10 +7306,14 @@
         <f t="shared" si="1"/>
         <v>7.91015625E-2</v>
       </c>
+      <c r="X29">
+        <f t="shared" si="5"/>
+        <v>0.28125</v>
+      </c>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>351.95000000000005</v>
       </c>
       <c r="C30">
@@ -7211,11 +7326,11 @@
         <v>800</v>
       </c>
       <c r="F30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20.449294252618483</v>
       </c>
       <c r="K30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>234.3</v>
       </c>
       <c r="L30">
@@ -7228,8 +7343,8 @@
         <v>800</v>
       </c>
       <c r="O30">
-        <f t="shared" si="10"/>
-        <v>4614.192257177071</v>
+        <f t="shared" si="11"/>
+        <v>46.141922571770706</v>
       </c>
       <c r="S30">
         <v>203</v>
@@ -7249,10 +7364,14 @@
         <f t="shared" si="1"/>
         <v>4.78515625E-2</v>
       </c>
+      <c r="X30">
+        <f t="shared" si="5"/>
+        <v>0.21875</v>
+      </c>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>315.7</v>
       </c>
       <c r="C31">
@@ -7265,11 +7384,11 @@
         <v>1000</v>
       </c>
       <c r="F31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>25.41505766925258</v>
       </c>
       <c r="K31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>210.15</v>
       </c>
       <c r="L31">
@@ -7282,8 +7401,8 @@
         <v>1000</v>
       </c>
       <c r="O31">
-        <f t="shared" si="10"/>
-        <v>5735.6345821710556</v>
+        <f t="shared" si="11"/>
+        <v>57.356345821710555</v>
       </c>
       <c r="S31">
         <v>201.4</v>
@@ -7302,6 +7421,10 @@
       <c r="W31">
         <f t="shared" si="1"/>
         <v>2.44140625E-2</v>
+      </c>
+      <c r="X31">
+        <f t="shared" si="5"/>
+        <v>0.15625</v>
       </c>
     </row>
   </sheetData>
@@ -7323,19 +7446,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
